--- a/attendance.xlsx
+++ b/attendance.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MATHS" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="AI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="maths" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Maths1" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,6 +415,222 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Karan</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Kaustubh</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ram</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sahil</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tejas</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Utkarsha</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Kaustubh</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -424,14 +642,14 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kaustubh</t>
+          <t>Karan</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -443,7 +661,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sahil</t>
+          <t>Kaustubh</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
